--- a/data/trans_dic/P15D$urgencias-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15D$urgencias-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,5; 73,24</t>
+          <t>14,92; 70,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,7; 74,2</t>
+          <t>38,17; 75,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,2; 74,46</t>
+          <t>25,29; 73,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,38; 78,15</t>
+          <t>35,39; 78,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,86; 100,0</t>
+          <t>31,77; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,02; 95,58</t>
+          <t>59,83; 95,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,15; 84,37</t>
+          <t>43,29; 87,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,01; 67,18</t>
+          <t>35,14; 65,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,41; 76,27</t>
+          <t>29,19; 75,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,95; 79,07</t>
+          <t>51,25; 79,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41,7; 72,69</t>
+          <t>41,21; 74,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,93; 67,91</t>
+          <t>40,47; 66,83</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,77; 68,89</t>
+          <t>15,07; 70,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,25; 73,19</t>
+          <t>37,34; 71,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,2; 83,73</t>
+          <t>40,78; 84,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,49; 78,76</t>
+          <t>34,46; 79,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,8; 76,53</t>
+          <t>33,74; 76,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,42; 95,06</t>
+          <t>52,55; 92,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,93; 62,29</t>
+          <t>30,15; 64,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,1; 62,52</t>
+          <t>16,16; 62,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,47; 67,68</t>
+          <t>42,84; 69,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,99; 85,45</t>
+          <t>55,22; 85,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,14; 65,93</t>
+          <t>36,16; 66,21</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,38; 65,31</t>
+          <t>29,27; 66,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,62; 75,52</t>
+          <t>48,34; 74,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,71; 69,03</t>
+          <t>34,0; 69,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,06; 70,33</t>
+          <t>37,14; 69,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,64</t>
+          <t>0,0; 78,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,34; 72,51</t>
+          <t>16,31; 73,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,74; 87,91</t>
+          <t>12,53; 87,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,93; 60,65</t>
+          <t>17,72; 62,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,06; 61,17</t>
+          <t>26,86; 65,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,95; 69,9</t>
+          <t>45,58; 69,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,61; 67,76</t>
+          <t>33,78; 66,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,72; 62,2</t>
+          <t>35,53; 62,75</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,77; 63,57</t>
+          <t>32,11; 65,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,79; 67,81</t>
+          <t>47,78; 67,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,98; 80,26</t>
+          <t>56,65; 80,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,27; 63,13</t>
+          <t>36,85; 62,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,93; 86,47</t>
+          <t>48,67; 86,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,06; 74,15</t>
+          <t>47,29; 74,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,15; 77,48</t>
+          <t>44,17; 77,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,56; 75,22</t>
+          <t>50,97; 74,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,87; 69,64</t>
+          <t>45,16; 70,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50,89; 66,76</t>
+          <t>50,03; 66,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,08; 75,98</t>
+          <t>56,38; 76,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,86; 64,05</t>
+          <t>46,96; 64,87</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,59; 81,39</t>
+          <t>22,3; 82,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,91; 73,22</t>
+          <t>38,6; 71,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,54; 70,5</t>
+          <t>38,39; 69,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,55; 80,03</t>
+          <t>46,68; 79,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,7; 91,66</t>
+          <t>53,38; 91,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,0; 66,07</t>
+          <t>39,3; 65,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,85; 73,49</t>
+          <t>41,91; 73,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,43; 58,68</t>
+          <t>36,32; 59,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49,16; 81,73</t>
+          <t>48,05; 82,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,19; 64,08</t>
+          <t>44,63; 63,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,11; 68,68</t>
+          <t>45,14; 66,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,89; 64,34</t>
+          <t>45,19; 64,33</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,21; 74,34</t>
+          <t>26,03; 75,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,62; 76,65</t>
+          <t>43,18; 78,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,32; 83,99</t>
+          <t>45,5; 81,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43,83; 100,0</t>
+          <t>54,44; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,39; 78,36</t>
+          <t>40,64; 77,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,6; 61,64</t>
+          <t>41,07; 61,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,51; 78,66</t>
+          <t>52,57; 78,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,57; 62,09</t>
+          <t>36,0; 61,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,05; 71,69</t>
+          <t>40,11; 70,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43,71; 61,44</t>
+          <t>43,92; 62,58</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55,31; 77,29</t>
+          <t>55,79; 76,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,07; 70,92</t>
+          <t>43,91; 70,35</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,28; 56,36</t>
+          <t>37,35; 56,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,06; 64,07</t>
+          <t>52,57; 64,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,48; 67,38</t>
+          <t>53,96; 67,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,93; 66,47</t>
+          <t>50,58; 65,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,64; 74,35</t>
+          <t>54,77; 75,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,01; 62,1</t>
+          <t>49,35; 62,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,09; 71,8</t>
+          <t>57,57; 71,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,82; 56,62</t>
+          <t>45,31; 56,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,87; 61,92</t>
+          <t>47,08; 61,37</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52,43; 61,04</t>
+          <t>52,96; 61,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57,64; 67,45</t>
+          <t>58,11; 68,37</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,72; 59,43</t>
+          <t>49,17; 59,4</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2078; 9227</t>
+          <t>1879; 8885</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12805; 25198</t>
+          <t>12963; 25644</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5428; 16035</t>
+          <t>5447; 15755</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8432; 18628</t>
+          <t>8434; 18627</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2317; 7761</t>
+          <t>2466; 7761</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10402; 16563</t>
+          <t>10369; 16516</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8861; 16934</t>
+          <t>8687; 17580</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8126; 15591</t>
+          <t>8155; 15232</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6190; 15527</t>
+          <t>5943; 15455</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26135; 40558</t>
+          <t>26286; 40833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17350; 30242</t>
+          <t>17146; 30993</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19726; 31950</t>
+          <t>19040; 31441</t>
         </is>
       </c>
     </row>
@@ -2135,22 +2135,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1962; 9149</t>
+          <t>2002; 9312</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12412; 23748</t>
+          <t>12115; 23219</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6946; 14116</t>
+          <t>6875; 14302</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7846; 19017</t>
+          <t>8321; 19128</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,37 +2160,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9344; 20551</t>
+          <t>9061; 20536</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12239; 20995</t>
+          <t>11606; 20504</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6931; 14425</t>
+          <t>6983; 14879</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3037; 11795</t>
+          <t>3050; 11730</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25188; 40134</t>
+          <t>25403; 41466</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21805; 33280</t>
+          <t>21508; 33180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17571; 31189</t>
+          <t>17107; 31321</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7744; 18472</t>
+          <t>8278; 18923</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27536; 42773</t>
+          <t>27379; 42438</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10474; 21445</t>
+          <t>10563; 21609</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12357; 23448</t>
+          <t>12382; 23227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3898</t>
+          <t>0; 3899</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2287; 10151</t>
+          <t>2284; 10242</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1121; 7735</t>
+          <t>1102; 7680</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2271; 7278</t>
+          <t>2126; 7557</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8996; 20335</t>
+          <t>8930; 21621</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33167; 49374</t>
+          <t>32199; 49211</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14196; 27011</t>
+          <t>13465; 26538</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16650; 28199</t>
+          <t>16108; 28451</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12396; 24807</t>
+          <t>12529; 25472</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44744; 64844</t>
+          <t>45687; 64903</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32433; 47349</t>
+          <t>33421; 47528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24779; 41976</t>
+          <t>24504; 41714</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12737; 21627</t>
+          <t>12173; 21709</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22423; 36097</t>
+          <t>23023; 36415</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17366; 29803</t>
+          <t>16990; 29684</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25029; 37235</t>
+          <t>25230; 37019</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28093; 44595</t>
+          <t>28919; 45047</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73430; 96339</t>
+          <t>72193; 95363</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54650; 74053</t>
+          <t>54948; 74370</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52030; 74288</t>
+          <t>54465; 75242</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2855; 10289</t>
+          <t>2819; 10408</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14893; 28028</t>
+          <t>14776; 27537</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16440; 29314</t>
+          <t>15964; 28966</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17450; 30659</t>
+          <t>17884; 30517</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11606; 20577</t>
+          <t>11983; 20604</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23293; 38469</t>
+          <t>22881; 38113</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17315; 29697</t>
+          <t>16935; 29543</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19353; 31175</t>
+          <t>19298; 31400</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17250; 28679</t>
+          <t>16861; 29102</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41679; 61838</t>
+          <t>43071; 61732</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37810; 56316</t>
+          <t>37009; 54716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>41046; 58830</t>
+          <t>41318; 58819</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4244; 12038</t>
+          <t>4215; 12185</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11702; 20562</t>
+          <t>11583; 21095</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13708; 24857</t>
+          <t>13468; 24241</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5141; 11729</t>
+          <t>6386; 11729</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11607; 21973</t>
+          <t>11396; 21801</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35341; 55020</t>
+          <t>36653; 54834</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31734; 47537</t>
+          <t>31768; 47456</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16590; 28960</t>
+          <t>16792; 28699</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18156; 31714</t>
+          <t>17742; 31376</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50738; 71315</t>
+          <t>50981; 72637</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49792; 69585</t>
+          <t>50232; 68923</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25138; 41397</t>
+          <t>25632; 41063</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>46709; 68776</t>
+          <t>45580; 68540</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>147737; 181822</t>
+          <t>149176; 181649</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106766; 134514</t>
+          <t>107727; 135418</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100772; 131511</t>
+          <t>100082; 130010</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>51253; 69745</t>
+          <t>51379; 70627</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>124644; 157938</t>
+          <t>125526; 158211</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>108617; 136617</t>
+          <t>109543; 136873</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>93057; 117573</t>
+          <t>94072; 117895</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>103311; 133633</t>
+          <t>101610; 132462</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>282136; 328442</t>
+          <t>284961; 331171</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>224745; 262987</t>
+          <t>226554; 266569</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>201611; 240994</t>
+          <t>199371; 240878</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$urgencias-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15D$urgencias-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,92; 70,53</t>
+          <t>14,68; 69,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,17; 75,51</t>
+          <t>37,41; 76,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,29; 73,16</t>
+          <t>27,42; 71,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,39; 78,15</t>
+          <t>41,29; 79,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,77; 100,0</t>
+          <t>35,65; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,83; 95,31</t>
+          <t>58,72; 95,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,29; 87,59</t>
+          <t>42,8; 85,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,14; 65,63</t>
+          <t>34,28; 64,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,19; 75,92</t>
+          <t>29,44; 76,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51,25; 79,61</t>
+          <t>51,49; 79,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41,21; 74,49</t>
+          <t>41,7; 73,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,47; 66,83</t>
+          <t>44,0; 68,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,99%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,07; 70,11</t>
+          <t>7,97; 64,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,34; 71,56</t>
+          <t>37,09; 73,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,78; 84,83</t>
+          <t>41,16; 83,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,46; 79,22</t>
+          <t>34,57; 76,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,74</t>
+          <t>0,0; 83,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,74; 76,47</t>
+          <t>34,52; 74,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,55; 92,84</t>
+          <t>54,09; 94,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,15; 64,25</t>
+          <t>31,66; 63,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,16; 62,17</t>
+          <t>16,19; 65,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,84; 69,92</t>
+          <t>41,24; 67,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,22; 85,2</t>
+          <t>54,27; 86,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,16; 66,21</t>
+          <t>38,89; 65,48</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>51,49%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,27; 66,9</t>
+          <t>29,03; 66,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,34; 74,93</t>
+          <t>46,9; 74,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,0; 69,56</t>
+          <t>33,0; 69,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,14; 69,67</t>
+          <t>40,66; 72,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,66</t>
+          <t>0,0; 80,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,31; 73,16</t>
+          <t>16,42; 71,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 87,29</t>
+          <t>22,76; 87,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,72; 62,98</t>
+          <t>17,78; 59,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,86; 65,04</t>
+          <t>26,44; 60,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,58; 69,67</t>
+          <t>45,5; 70,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,78; 66,57</t>
+          <t>36,69; 67,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,53; 62,75</t>
+          <t>37,58; 64,01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>59,09%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,11; 65,27</t>
+          <t>31,14; 63,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,78; 67,88</t>
+          <t>47,48; 67,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,65; 80,57</t>
+          <t>56,51; 80,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,85; 62,74</t>
+          <t>40,8; 65,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,67; 86,8</t>
+          <t>49,87; 87,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,29; 74,81</t>
+          <t>46,42; 74,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,17; 77,17</t>
+          <t>45,56; 77,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,97; 74,78</t>
+          <t>52,76; 76,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45,16; 70,35</t>
+          <t>44,86; 70,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50,03; 66,09</t>
+          <t>50,02; 66,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,38; 76,31</t>
+          <t>56,02; 75,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,96; 64,87</t>
+          <t>49,03; 67,36</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,58%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,3; 82,34</t>
+          <t>24,43; 81,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,6; 71,94</t>
+          <t>40,18; 72,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,39; 69,66</t>
+          <t>39,98; 71,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46,68; 79,66</t>
+          <t>47,0; 79,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>53,38; 91,78</t>
+          <t>52,34; 91,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,3; 65,46</t>
+          <t>38,25; 65,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,91; 73,11</t>
+          <t>42,36; 73,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,32; 59,11</t>
+          <t>35,17; 59,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,05; 82,94</t>
+          <t>45,95; 82,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,63; 63,97</t>
+          <t>43,57; 63,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,14; 66,73</t>
+          <t>45,76; 67,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,19; 64,33</t>
+          <t>45,4; 65,38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,03; 75,25</t>
+          <t>27,04; 76,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,18; 78,64</t>
+          <t>40,69; 78,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,5; 81,91</t>
+          <t>46,4; 82,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54,44; 100,0</t>
+          <t>35,89; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,64; 77,74</t>
+          <t>41,33; 78,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,07; 61,44</t>
+          <t>39,83; 60,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,57; 78,52</t>
+          <t>53,0; 78,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,0; 61,53</t>
+          <t>36,51; 63,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40,11; 70,93</t>
+          <t>41,61; 71,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43,92; 62,58</t>
+          <t>42,95; 61,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55,79; 76,55</t>
+          <t>55,4; 76,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,91; 70,35</t>
+          <t>41,64; 67,9</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,83%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,35; 56,17</t>
+          <t>36,9; 55,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,57; 64,01</t>
+          <t>51,59; 64,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,96; 67,83</t>
+          <t>53,55; 67,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,58; 65,71</t>
+          <t>51,97; 66,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,77; 75,29</t>
+          <t>54,18; 73,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,35; 62,2</t>
+          <t>48,52; 60,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,57; 71,94</t>
+          <t>57,41; 71,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,31; 56,78</t>
+          <t>46,1; 58,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,08; 61,37</t>
+          <t>47,45; 61,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52,96; 61,54</t>
+          <t>52,23; 61,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58,11; 68,37</t>
+          <t>57,67; 67,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,17; 59,4</t>
+          <t>50,9; 60,6</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>29134</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1879; 8885</t>
+          <t>1849; 8732</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12963; 25644</t>
+          <t>12706; 25876</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5447; 15755</t>
+          <t>5906; 15445</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8434; 18627</t>
+          <t>10680; 20678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2466; 7761</t>
+          <t>2767; 7761</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10369; 16516</t>
+          <t>10175; 16503</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8687; 17580</t>
+          <t>8589; 17215</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8155; 15232</t>
+          <t>8976; 16923</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5943; 15455</t>
+          <t>5993; 15643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26286; 40833</t>
+          <t>26407; 40731</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17146; 30993</t>
+          <t>17349; 30427</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19040; 31441</t>
+          <t>22904; 35684</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25076</t>
+          <t>26875</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2002; 9312</t>
+          <t>1058; 8591</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12115; 23219</t>
+          <t>12035; 23811</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6875; 14302</t>
+          <t>6940; 14081</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8321; 19128</t>
+          <t>8896; 19761</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4624</t>
+          <t>0; 4648</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9061; 20536</t>
+          <t>9269; 20051</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11606; 20504</t>
+          <t>11947; 20942</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6983; 14879</t>
+          <t>7909; 15871</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3050; 11730</t>
+          <t>3055; 12385</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25403; 41466</t>
+          <t>24456; 40312</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21508; 33180</t>
+          <t>21135; 33578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17107; 31321</t>
+          <t>19723; 33207</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18093</t>
+          <t>21021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22657</t>
+          <t>25722</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8278; 18923</t>
+          <t>8211; 18816</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27379; 42438</t>
+          <t>26563; 42202</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10563; 21609</t>
+          <t>10252; 21716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12382; 23227</t>
+          <t>15155; 26983</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3899</t>
+          <t>0; 3986</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2284; 10242</t>
+          <t>2299; 10066</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1102; 7680</t>
+          <t>2002; 7731</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2126; 7557</t>
+          <t>2256; 7554</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8930; 21621</t>
+          <t>8790; 20230</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32199; 49211</t>
+          <t>32142; 49562</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13465; 26538</t>
+          <t>14625; 26810</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16108; 28451</t>
+          <t>18773; 31979</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33375</t>
+          <t>42686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31281</t>
+          <t>36005</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>78690</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12529; 25472</t>
+          <t>12151; 24726</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45687; 64903</t>
+          <t>45399; 64859</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33421; 47528</t>
+          <t>33334; 47664</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24504; 41714</t>
+          <t>31733; 51039</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12173; 21709</t>
+          <t>12474; 21798</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23023; 36415</t>
+          <t>22598; 36048</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16990; 29684</t>
+          <t>17523; 29702</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25230; 37019</t>
+          <t>29228; 42120</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28919; 45047</t>
+          <t>28725; 44995</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72193; 95363</t>
+          <t>72178; 96554</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54948; 74370</t>
+          <t>54600; 73522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54465; 75242</t>
+          <t>65295; 89703</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>26441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25234</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50132</t>
+          <t>54065</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2819; 10408</t>
+          <t>3089; 10287</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14776; 27537</t>
+          <t>15379; 27868</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15964; 28966</t>
+          <t>16627; 29676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17884; 30517</t>
+          <t>18952; 32201</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11983; 20604</t>
+          <t>11749; 20513</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22881; 38113</t>
+          <t>22274; 37983</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16935; 29543</t>
+          <t>17117; 29541</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19298; 31400</t>
+          <t>20034; 33757</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16861; 29102</t>
+          <t>16122; 29083</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43071; 61732</t>
+          <t>42049; 61680</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37009; 54716</t>
+          <t>37522; 55536</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>41318; 58819</t>
+          <t>44170; 63605</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22282</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>33159</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4215; 12185</t>
+          <t>4379; 12357</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11583; 21095</t>
+          <t>10916; 21112</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13468; 24241</t>
+          <t>13732; 24483</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6386; 11729</t>
+          <t>4028; 11222</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11396; 21801</t>
+          <t>11589; 21937</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36653; 54834</t>
+          <t>35547; 54133</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31768; 47456</t>
+          <t>32033; 47362</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16792; 28699</t>
+          <t>17962; 31070</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17742; 31376</t>
+          <t>18408; 31534</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50981; 72637</t>
+          <t>49852; 71573</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50232; 68923</t>
+          <t>49876; 68648</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25632; 41063</t>
+          <t>25156; 41026</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115708</t>
+          <t>130144</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>105799</t>
+          <t>117502</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>221507</t>
+          <t>247645</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45580; 68540</t>
+          <t>45021; 67622</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>149176; 181649</t>
+          <t>146400; 181897</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>107727; 135418</t>
+          <t>106898; 135360</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100082; 130010</t>
+          <t>113387; 145645</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>51379; 70627</t>
+          <t>50824; 69211</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>125526; 158211</t>
+          <t>123411; 153519</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>109543; 136873</t>
+          <t>109229; 136949</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>94072; 117895</t>
+          <t>103923; 130872</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>101610; 132462</t>
+          <t>102408; 132182</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>284961; 331171</t>
+          <t>281031; 329930</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>226554; 266569</t>
+          <t>224871; 263315</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>199371; 240878</t>
+          <t>225810; 268820</t>
         </is>
       </c>
     </row>
